--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_apoyopot_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_apoyopot_a_2022.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:34</t>
+    <t xml:space="preserve">2026-09-24 01:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -806,10 +806,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -820,10 +820,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -834,10 +834,10 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_apoyopot_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_apoyopot_a_2022.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:24</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_apoyopot_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_apoyopot_a_2022.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
